--- a/cellstocks/exports/grid-roster.xlsx
+++ b/cellstocks/exports/grid-roster.xlsx
@@ -66757,6 +66757,61 @@
           <t xml:space="preserve">G2</t>
         </is>
       </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCX</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cell</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Par</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CASPEX</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+24</t>
+        </is>
+      </c>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -66769,6 +66824,61 @@
           <t xml:space="preserve">G3</t>
         </is>
       </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCX</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cell</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Par</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CASPEX</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+24</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -66781,6 +66891,61 @@
           <t xml:space="preserve">G4</t>
         </is>
       </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCX</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cell</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Par</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CASPEX</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+24</t>
+        </is>
+      </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -66910,6 +67075,61 @@
           <t xml:space="preserve">H2</t>
         </is>
       </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUCX</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cell</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LuCap35CR</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CASPEX</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p21</t>
+        </is>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -66920,6 +67140,61 @@
       <c r="B391" t="inlineStr">
         <is>
           <t xml:space="preserve">H3</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUCX</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cell</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LuCap35CR</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CASPEX</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p21</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
         </is>
       </c>
     </row>
@@ -68127,17 +68402,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-11</t>
+          <t xml:space="preserve">2026-09-15T08:59:29.978Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">LUCX</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -68148,33 +68423,23 @@
       <c r="E2" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 H1</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-10</t>
+          <t xml:space="preserve">2026-09-15T08:59:29.978Z</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LUCX</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -68185,23 +68450,13 @@
       <c r="E3" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 F6</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09T13:48:02.210Z</t>
+          <t xml:space="preserve">2026-09-15T08:59:29.978Z</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -68211,7 +68466,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">deneme</t>
+          <t xml:space="preserve">LUCX</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -68221,14 +68476,14 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09T13:48:02.210Z</t>
+          <t xml:space="preserve">2026-09-15T08:59:01.686Z</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -68238,7 +68493,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">deneme</t>
+          <t xml:space="preserve">LNCX</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -68255,7 +68510,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09T04:57:21.749Z</t>
+          <t xml:space="preserve">2026-09-15T08:59:01.686Z</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -68265,7 +68520,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">LNCX</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -68275,14 +68530,14 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09T04:57:21.749Z</t>
+          <t xml:space="preserve">2026-09-15T08:59:01.686Z</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -68292,7 +68547,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">LNCX</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -68309,12 +68564,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09T04:57:19.918Z</t>
+          <t xml:space="preserve">2026-09-11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -68329,24 +68584,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 H1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09T04:57:19.918Z</t>
+          <t xml:space="preserve">2026-09-10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -68357,13 +68622,23 @@
       <c r="E9" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 F6</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09T04:57:16.692Z</t>
+          <t xml:space="preserve">2026-09-09T13:48:02.210Z</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -68373,7 +68648,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">deneme</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -68390,7 +68665,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09T04:57:16.692Z</t>
+          <t xml:space="preserve">2026-09-09T13:48:02.210Z</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -68400,7 +68675,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">deneme</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -68417,17 +68692,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-09T04:57:21.749Z</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">kkk</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -68438,33 +68713,23 @@
       <c r="E12" t="inlineStr">
         <is>
           <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-09T04:57:21.749Z</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">kkk</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -68474,34 +68739,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A3</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-09T04:57:19.918Z</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">kkk</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -68512,33 +68767,23 @@
       <c r="E14" t="inlineStr">
         <is>
           <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A2</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-09T04:57:19.918Z</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">kkk</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -68548,29 +68793,19 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A1</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-09T04:57:16.692Z</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -68586,28 +68821,18 @@
       <c r="E16" t="inlineStr">
         <is>
           <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 H3</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-09T04:57:16.692Z</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -68622,17 +68847,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 H2</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
@@ -68649,7 +68864,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">deneme</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -68664,7 +68879,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 B3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -68696,12 +68911,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -68733,12 +68948,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -68760,7 +68975,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -68770,12 +68985,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -68797,7 +69012,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">kkk</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -68807,12 +69022,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A1</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 H3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -68844,12 +69059,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 H3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 H2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -68871,7 +69086,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">deneme</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -68881,12 +69096,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 H2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 B3</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -68908,7 +69123,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">deneme</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -68923,7 +69138,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 B3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -68935,17 +69150,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T20:53:21.794Z</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">khk</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -68955,24 +69170,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A3</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T20:53:21.794Z</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">khk</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -68983,23 +69208,33 @@
       <c r="E27" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A2</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T20:05:13.592Z</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -69009,24 +69244,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A1</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T20:05:13.592Z</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">kkk</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -69036,24 +69281,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 H3</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T20:05:13.592Z</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">kkk</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -69063,24 +69318,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 H2</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T20:05:13.592Z</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">deneme</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -69091,13 +69356,23 @@
       <c r="E31" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 B3</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T20:05:13.592Z</t>
+          <t xml:space="preserve">2026-09-08T20:53:21.794Z</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -69107,7 +69382,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">khk</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -69117,14 +69392,14 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T20:05:13.592Z</t>
+          <t xml:space="preserve">2026-09-08T20:53:21.794Z</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -69134,7 +69409,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">khk</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -69151,7 +69426,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T18:36:51.554Z</t>
+          <t xml:space="preserve">2026-09-08T20:05:13.592Z</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -69161,7 +69436,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -69178,7 +69453,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T18:36:51.554Z</t>
+          <t xml:space="preserve">2026-09-08T20:05:13.592Z</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -69188,7 +69463,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -69198,14 +69473,14 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T11:09:47.786Z</t>
+          <t xml:space="preserve">2026-09-08T20:05:13.592Z</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -69215,7 +69490,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hek caspex</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -69232,7 +69507,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T11:09:47.786Z</t>
+          <t xml:space="preserve">2026-09-08T20:05:13.592Z</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -69242,7 +69517,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hek caspex</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -69259,17 +69534,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-08T20:05:13.592Z</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hek caspex</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -69279,34 +69554,24 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 I8</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-08T20:05:13.592Z</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -69316,34 +69581,24 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-08T18:36:51.554Z</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -69354,33 +69609,23 @@
       <c r="E40" t="inlineStr">
         <is>
           <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A6</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-08T18:36:51.554Z</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -69390,34 +69635,24 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A8</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-08T11:09:47.786Z</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 gNT</t>
+          <t xml:space="preserve">Hek caspex</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -69428,33 +69663,23 @@
       <c r="E42" t="inlineStr">
         <is>
           <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 E6</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-08T11:09:47.786Z</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">Hek caspex</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -69464,17 +69689,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 E8</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
@@ -69491,7 +69706,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">Hek caspex</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -69506,7 +69721,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 B8</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 I8</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -69528,7 +69743,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -69543,7 +69758,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 D5</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -69565,7 +69780,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -69580,7 +69795,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 D3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A6</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -69602,7 +69817,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">khk</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -69617,7 +69832,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 D4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A8</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -69639,7 +69854,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">Huh7 gNT</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -69654,7 +69869,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A1</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 E6</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -69676,7 +69891,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -69691,7 +69906,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 E8</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -69713,7 +69928,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -69728,7 +69943,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 B8</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -69750,7 +69965,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -69765,7 +69980,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 D5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -69787,7 +70002,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -69802,7 +70017,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A1</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 D3</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -69824,7 +70039,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">khk</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -69839,7 +70054,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 D4</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -70009,7 +70224,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -70024,7 +70239,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A1</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -70061,7 +70276,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A2</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -70083,7 +70298,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -70098,7 +70313,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A1</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -70120,7 +70335,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -70135,7 +70350,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A1</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A2</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -70172,7 +70387,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A3</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -70209,7 +70424,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -70320,7 +70535,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A2</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -70342,7 +70557,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hek caspex</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -70352,12 +70567,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 I8</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A1</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -70379,7 +70594,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -70389,7 +70604,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -70416,7 +70631,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -70426,12 +70641,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A6</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A3</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -70453,7 +70668,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -70463,12 +70678,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A8</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -70490,7 +70705,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 gNT</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -70500,12 +70715,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 E6</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A3</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -70527,7 +70742,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -70537,12 +70752,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 E8</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -70564,7 +70779,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">Hek caspex</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -70579,7 +70794,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 B8</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 I8</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -70601,7 +70816,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -70616,7 +70831,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 D5</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -70638,7 +70853,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -70653,7 +70868,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 D3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A6</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -70675,7 +70890,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">khk</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -70690,7 +70905,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 D4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A8</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -70712,7 +70927,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">Huh7 gNT</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -70727,7 +70942,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A1</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 E6</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -70749,7 +70964,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -70764,7 +70979,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 E8</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -70786,7 +71001,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -70801,7 +71016,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 B8</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -70823,7 +71038,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -70838,7 +71053,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 D5</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -70860,7 +71075,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -70875,7 +71090,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A1</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 D3</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -70897,7 +71112,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">khk</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -70912,7 +71127,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 D4</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -71082,7 +71297,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -71097,7 +71312,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A1</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -71134,7 +71349,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A2</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -71156,7 +71371,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -71171,7 +71386,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A1</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -71193,7 +71408,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -71208,7 +71423,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A1</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A2</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -71245,7 +71460,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A3</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -71282,7 +71497,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -71393,7 +71608,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A2</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -71405,17 +71620,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:21:12.672Z</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -71425,24 +71640,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A1</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:21:12.672Z</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -71452,24 +71677,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:21:12.672Z</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -71480,23 +71715,33 @@
       <c r="E98" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A3</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:21:12.672Z</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -71507,23 +71752,33 @@
       <c r="E99" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:20:40.838Z</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -71533,24 +71788,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A3</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:20:40.838Z</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -71560,14 +71825,24 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:20:40.838Z</t>
+          <t xml:space="preserve">2026-09-07T15:21:12.672Z</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -71577,7 +71852,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -71587,14 +71862,14 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:20:40.838Z</t>
+          <t xml:space="preserve">2026-09-07T15:21:12.672Z</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -71604,7 +71879,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -71614,14 +71889,14 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:20:16.472Z</t>
+          <t xml:space="preserve">2026-09-07T15:21:12.672Z</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -71631,7 +71906,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -71641,14 +71916,14 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:20:16.472Z</t>
+          <t xml:space="preserve">2026-09-07T15:21:12.672Z</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -71658,7 +71933,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -71668,14 +71943,14 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:20:16.472Z</t>
+          <t xml:space="preserve">2026-09-07T15:20:40.838Z</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -71685,7 +71960,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -71695,14 +71970,14 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:20:16.472Z</t>
+          <t xml:space="preserve">2026-09-07T15:20:40.838Z</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -71712,7 +71987,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -71722,14 +71997,14 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:19:46.171Z</t>
+          <t xml:space="preserve">2026-09-07T15:20:40.838Z</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -71739,7 +72014,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 gNT</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -71749,14 +72024,14 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:19:46.171Z</t>
+          <t xml:space="preserve">2026-09-07T15:20:40.838Z</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -71766,7 +72041,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 gNT</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -71776,14 +72051,14 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:19:46.171Z</t>
+          <t xml:space="preserve">2026-09-07T15:20:16.472Z</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -71793,7 +72068,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 gNT</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -71803,14 +72078,14 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:19:46.171Z</t>
+          <t xml:space="preserve">2026-09-07T15:20:16.472Z</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -71820,7 +72095,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 gNT</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -71830,14 +72105,14 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:19:15.021Z</t>
+          <t xml:space="preserve">2026-09-07T15:20:16.472Z</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -71847,7 +72122,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -71857,14 +72132,14 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:19:15.021Z</t>
+          <t xml:space="preserve">2026-09-07T15:20:16.472Z</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -71874,7 +72149,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek atf3 ox rep3</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -71884,14 +72159,14 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:19:15.021Z</t>
+          <t xml:space="preserve">2026-09-07T15:19:46.171Z</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -71901,7 +72176,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">Huh7 gNT</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -71911,14 +72186,14 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:19:15.021Z</t>
+          <t xml:space="preserve">2026-09-07T15:19:46.171Z</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -71928,7 +72203,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek atf3 ox rep3</t>
+          <t xml:space="preserve">Huh7 gNT</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -71938,14 +72213,14 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:18:48.988Z</t>
+          <t xml:space="preserve">2026-09-07T15:19:46.171Z</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -71955,7 +72230,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">Huh7 gNT</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -71965,14 +72240,14 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:18:48.988Z</t>
+          <t xml:space="preserve">2026-09-07T15:19:46.171Z</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -71982,7 +72257,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">Huh7 gNT</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -71992,14 +72267,14 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:18:48.988Z</t>
+          <t xml:space="preserve">2026-09-07T15:19:15.021Z</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -72009,7 +72284,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -72019,14 +72294,14 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:18:48.988Z</t>
+          <t xml:space="preserve">2026-09-07T15:19:15.021Z</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -72036,7 +72311,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">hek atf3 ox rep3</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -72046,14 +72321,14 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:18:16.654Z</t>
+          <t xml:space="preserve">2026-09-07T15:19:15.021Z</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -72063,7 +72338,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -72073,14 +72348,14 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:18:16.654Z</t>
+          <t xml:space="preserve">2026-09-07T15:19:15.021Z</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -72090,7 +72365,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">hek atf3 ox rep3</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -72100,14 +72375,14 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:18:16.654Z</t>
+          <t xml:space="preserve">2026-09-07T15:18:48.988Z</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -72117,7 +72392,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -72127,14 +72402,14 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:18:16.654Z</t>
+          <t xml:space="preserve">2026-09-07T15:18:48.988Z</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -72144,7 +72419,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -72154,14 +72429,14 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:17:40.188Z</t>
+          <t xml:space="preserve">2026-09-07T15:18:48.988Z</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -72171,7 +72446,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -72181,14 +72456,14 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:17:40.188Z</t>
+          <t xml:space="preserve">2026-09-07T15:18:48.988Z</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -72198,7 +72473,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -72208,14 +72483,14 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:17:40.188Z</t>
+          <t xml:space="preserve">2026-09-07T15:18:16.654Z</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -72225,7 +72500,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -72235,32 +72510,194 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
+          <t xml:space="preserve">2026-09-07T15:18:16.654Z</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">added</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown device</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07T15:18:16.654Z</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">added</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown device</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07T15:18:16.654Z</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">added</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown device</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-07T15:17:40.188Z</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
+      <c r="B130" t="inlineStr">
         <is>
           <t xml:space="preserve">added</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
+      <c r="C130" t="inlineStr">
         <is>
           <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
+      <c r="D130" t="inlineStr">
         <is>
           <t xml:space="preserve">unknown device</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
+      <c r="E130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07T15:17:40.188Z</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">added</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK gNT</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown device</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07T15:17:40.188Z</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">added</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK gNT</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown device</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07T15:17:40.188Z</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">added</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK gNT</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown device</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
         </is>

--- a/cellstocks/exports/grid-roster.xlsx
+++ b/cellstocks/exports/grid-roster.xlsx
@@ -56515,6 +56515,61 @@
           <t xml:space="preserve">E6</t>
         </is>
       </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 gNT</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cell</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Par</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gNT</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p19</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-17</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-17</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -56594,6 +56649,61 @@
           <t xml:space="preserve">E8</t>
         </is>
       </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cell</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KO</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Par</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p19</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-17</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-17</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -58891,6 +59001,61 @@
           <t xml:space="preserve">I8</t>
         </is>
       </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK gNT</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cell</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Par</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gNT</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p23</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-17</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-17</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -64288,6 +64453,61 @@
           <t xml:space="preserve">A4</t>
         </is>
       </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK 3xFLAG</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cell</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FLAG</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Par</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p22</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-17</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-17</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -64367,6 +64587,61 @@
           <t xml:space="preserve">A6</t>
         </is>
       </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cell</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OX</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Par</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p29</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-17</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-17</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -64979,6 +65254,61 @@
           <t xml:space="preserve">B8</t>
         </is>
       </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cell</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KO</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Par</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p26</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-17</t>
+        </is>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-17</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -65795,6 +66125,61 @@
           <t xml:space="preserve">D3</t>
         </is>
       </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cell</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FLAG</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Par</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p19</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-17</t>
+        </is>
+      </c>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-17</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -65872,6 +66257,61 @@
       <c r="B357" t="inlineStr">
         <is>
           <t xml:space="preserve">D5</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cell</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OX</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Par</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p19</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-17</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-17</t>
         </is>
       </c>
     </row>
@@ -69127,7 +69567,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16T14:29:52.847Z</t>
+          <t xml:space="preserve">2026-09-17T08:55:14.517Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -69137,7 +69577,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gC4</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -69154,7 +69594,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16T14:29:52.847Z</t>
+          <t xml:space="preserve">2026-09-17T08:54:58.904Z</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -69164,7 +69604,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gC4</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -69181,7 +69621,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16T14:29:47.171Z</t>
+          <t xml:space="preserve">2026-09-17T08:54:36.349Z</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -69191,7 +69631,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gC3</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -69208,7 +69648,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16T14:29:47.171Z</t>
+          <t xml:space="preserve">2026-09-17T08:54:15.940Z</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -69218,7 +69658,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gC3</t>
+          <t xml:space="preserve">Huh7 gNT</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -69235,7 +69675,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16T14:29:41.829Z</t>
+          <t xml:space="preserve">2026-09-17T07:21:14.755Z</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -69245,7 +69685,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gC2</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -69262,7 +69702,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16T14:29:41.829Z</t>
+          <t xml:space="preserve">2026-09-17T07:20:55.862Z</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -69272,7 +69712,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gC2</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -69289,7 +69729,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16T14:28:53.172Z</t>
+          <t xml:space="preserve">2026-09-17T07:20:29.694Z</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -69299,7 +69739,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gC1</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -69316,7 +69756,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16T14:28:52.574Z</t>
+          <t xml:space="preserve">2026-09-17T07:18:28.049Z</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -69326,7 +69766,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gC1</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -69343,7 +69783,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16T14:28:36.457Z</t>
+          <t xml:space="preserve">2026-09-16T14:29:52.847Z</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -69353,7 +69793,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP3</t>
+          <t xml:space="preserve">LNCX gC4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -69370,7 +69810,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16T14:28:33.812Z</t>
+          <t xml:space="preserve">2026-09-16T14:29:52.847Z</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -69380,7 +69820,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP3</t>
+          <t xml:space="preserve">LNCX gC4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -69397,7 +69837,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16T14:28:18.882Z</t>
+          <t xml:space="preserve">2026-09-16T14:29:47.171Z</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -69407,7 +69847,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">LNCX gC3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -69424,7 +69864,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16T14:28:18.882Z</t>
+          <t xml:space="preserve">2026-09-16T14:29:47.171Z</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -69434,7 +69874,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">LNCX gC3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -69451,7 +69891,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16T14:28:08.430Z</t>
+          <t xml:space="preserve">2026-09-16T14:29:41.829Z</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -69461,7 +69901,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP1</t>
+          <t xml:space="preserve">LNCX gC2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -69478,7 +69918,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16T14:28:08.430Z</t>
+          <t xml:space="preserve">2026-09-16T14:29:41.829Z</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -69488,7 +69928,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP1</t>
+          <t xml:space="preserve">LNCX gC2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -69505,7 +69945,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-15T08:59:29.978Z</t>
+          <t xml:space="preserve">2026-09-16T14:28:53.172Z</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -69515,7 +69955,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX</t>
+          <t xml:space="preserve">LNCX gC1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -69525,14 +69965,14 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-15T08:59:29.978Z</t>
+          <t xml:space="preserve">2026-09-16T14:28:52.574Z</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -69542,7 +69982,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX</t>
+          <t xml:space="preserve">LNCX gC1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -69552,14 +69992,14 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-15T08:59:29.978Z</t>
+          <t xml:space="preserve">2026-09-16T14:28:36.457Z</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -69569,7 +70009,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX</t>
+          <t xml:space="preserve">LNCX gP3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -69579,14 +70019,14 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-15T08:59:29.978Z</t>
+          <t xml:space="preserve">2026-09-16T14:28:33.812Z</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -69596,7 +70036,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX</t>
+          <t xml:space="preserve">LNCX gP3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -69613,7 +70053,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-15T08:59:29.978Z</t>
+          <t xml:space="preserve">2026-09-16T14:28:18.882Z</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -69623,7 +70063,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -69640,7 +70080,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-15T08:59:29.978Z</t>
+          <t xml:space="preserve">2026-09-16T14:28:18.882Z</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -69650,7 +70090,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -69667,7 +70107,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-15T08:59:01.686Z</t>
+          <t xml:space="preserve">2026-09-16T14:28:08.430Z</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -69677,7 +70117,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX</t>
+          <t xml:space="preserve">LNCX gP1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -69687,14 +70127,14 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-15T08:59:01.686Z</t>
+          <t xml:space="preserve">2026-09-16T14:28:08.430Z</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -69704,7 +70144,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX</t>
+          <t xml:space="preserve">LNCX gP1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -69714,14 +70154,14 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-15T08:59:01.686Z</t>
+          <t xml:space="preserve">2026-09-15T08:59:29.978Z</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -69731,7 +70171,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX</t>
+          <t xml:space="preserve">LUCX</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -69748,7 +70188,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-15T08:59:01.686Z</t>
+          <t xml:space="preserve">2026-09-15T08:59:29.978Z</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -69758,7 +70198,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX</t>
+          <t xml:space="preserve">LUCX</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -69768,14 +70208,14 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-15T08:59:01.686Z</t>
+          <t xml:space="preserve">2026-09-15T08:59:29.978Z</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -69785,7 +70225,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX</t>
+          <t xml:space="preserve">LUCX</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -69795,14 +70235,14 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-15T08:59:01.686Z</t>
+          <t xml:space="preserve">2026-09-15T08:59:29.978Z</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -69812,7 +70252,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX</t>
+          <t xml:space="preserve">LUCX</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -69829,17 +70269,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-11</t>
+          <t xml:space="preserve">2026-09-15T08:59:29.978Z</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">LUCX</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -69849,34 +70289,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 H1</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-11</t>
+          <t xml:space="preserve">2026-09-15T08:59:29.978Z</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">LUCX</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -69887,33 +70317,23 @@
       <c r="E29" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 H1</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-10</t>
+          <t xml:space="preserve">2026-09-15T08:59:01.686Z</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LNCX</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -69924,33 +70344,23 @@
       <c r="E30" t="inlineStr">
         <is>
           <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 F6</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-10</t>
+          <t xml:space="preserve">2026-09-15T08:59:01.686Z</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LNCX</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -69960,24 +70370,14 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 F6</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09T13:48:02.210Z</t>
+          <t xml:space="preserve">2026-09-15T08:59:01.686Z</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -69987,7 +70387,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">deneme</t>
+          <t xml:space="preserve">LNCX</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -70004,7 +70404,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09T13:48:02.210Z</t>
+          <t xml:space="preserve">2026-09-15T08:59:01.686Z</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -70014,7 +70414,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">deneme</t>
+          <t xml:space="preserve">LNCX</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -70031,7 +70431,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09T04:57:21.749Z</t>
+          <t xml:space="preserve">2026-09-15T08:59:01.686Z</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -70041,7 +70441,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">LNCX</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -70051,14 +70451,14 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09T04:57:21.749Z</t>
+          <t xml:space="preserve">2026-09-15T08:59:01.686Z</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -70068,7 +70468,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">LNCX</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -70085,12 +70485,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09T04:57:19.918Z</t>
+          <t xml:space="preserve">2026-09-11</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -70106,18 +70506,28 @@
       <c r="E36" t="inlineStr">
         <is>
           <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 H1</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09T04:57:19.918Z</t>
+          <t xml:space="preserve">2026-09-11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -70133,23 +70543,33 @@
       <c r="E37" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 H1</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09T04:57:16.692Z</t>
+          <t xml:space="preserve">2026-09-10</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -70160,23 +70580,33 @@
       <c r="E38" t="inlineStr">
         <is>
           <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 F6</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09T04:57:16.692Z</t>
+          <t xml:space="preserve">2026-09-10</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -70187,23 +70617,33 @@
       <c r="E39" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 F6</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-09T13:48:02.210Z</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">deneme</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -70214,33 +70654,23 @@
       <c r="E40" t="inlineStr">
         <is>
           <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-09T13:48:02.210Z</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">deneme</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -70250,34 +70680,24 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-09T04:57:21.749Z</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">kkk</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -70288,33 +70708,23 @@
       <c r="E42" t="inlineStr">
         <is>
           <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-09T04:57:21.749Z</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">kkk</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -70324,29 +70734,19 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-09T04:57:19.918Z</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -70362,28 +70762,18 @@
       <c r="E44" t="inlineStr">
         <is>
           <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 H3</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-09T04:57:19.918Z</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -70398,34 +70788,24 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 H2</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-09T04:57:16.692Z</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">deneme</t>
+          <t xml:space="preserve">kkk</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -70436,33 +70816,23 @@
       <c r="E46" t="inlineStr">
         <is>
           <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 B3</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-09T04:57:16.692Z</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">kkk</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -70473,16 +70843,6 @@
       <c r="E47" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
@@ -70509,12 +70869,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -70546,12 +70906,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -70573,7 +70933,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -70583,12 +70943,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -70610,7 +70970,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -70620,12 +70980,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 H3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -70657,12 +71017,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 H2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 H3</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -70684,7 +71044,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">deneme</t>
+          <t xml:space="preserve">kkk</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -70694,12 +71054,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 B3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 H2</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -70711,17 +71071,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T20:53:21.794Z</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">khk</t>
+          <t xml:space="preserve">deneme</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -70732,23 +71092,33 @@
       <c r="E54" t="inlineStr">
         <is>
           <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 2 B3</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T20:53:21.794Z</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">khk</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -70759,18 +71129,28 @@
       <c r="E55" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T20:05:13.592Z</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -70785,19 +71165,29 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T20:05:13.592Z</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -70812,24 +71202,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T20:05:13.592Z</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -70839,24 +71239,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T20:05:13.592Z</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">kkk</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -70867,23 +71277,33 @@
       <c r="E59" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 H3</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T20:05:13.592Z</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">kkk</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -70894,23 +71314,33 @@
       <c r="E60" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 H2</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T20:05:13.592Z</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">deneme</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -70921,13 +71351,23 @@
       <c r="E61" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 2 B3</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T18:36:51.554Z</t>
+          <t xml:space="preserve">2026-09-08T20:53:21.794Z</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -70937,7 +71377,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">khk</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -70954,7 +71394,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T18:36:51.554Z</t>
+          <t xml:space="preserve">2026-09-08T20:53:21.794Z</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -70964,7 +71404,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">khk</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -70981,7 +71421,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T11:09:47.786Z</t>
+          <t xml:space="preserve">2026-09-08T20:05:13.592Z</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -70991,7 +71431,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hek caspex</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -71008,7 +71448,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T11:09:47.786Z</t>
+          <t xml:space="preserve">2026-09-08T20:05:13.592Z</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -71018,7 +71458,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hek caspex</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -71028,24 +71468,24 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-08T20:05:13.592Z</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hek caspex</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -71056,33 +71496,23 @@
       <c r="E66" t="inlineStr">
         <is>
           <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 I8</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-08T20:05:13.592Z</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -71092,34 +71522,24 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-08T20:05:13.592Z</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -71129,34 +71549,24 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A6</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-08T20:05:13.592Z</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -71166,34 +71576,24 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A8</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-08T18:36:51.554Z</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 gNT</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -71204,33 +71604,23 @@
       <c r="E70" t="inlineStr">
         <is>
           <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 E6</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-08T18:36:51.554Z</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -71240,34 +71630,24 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 E8</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-08T11:09:47.786Z</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">Hek caspex</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -71278,33 +71658,23 @@
       <c r="E72" t="inlineStr">
         <is>
           <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 B8</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-08T11:09:47.786Z</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">Hek caspex</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -71314,17 +71684,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 D5</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
@@ -71341,7 +71701,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">Hek caspex</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -71356,7 +71716,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 D3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 I8</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -71378,7 +71738,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">khk</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -71393,7 +71753,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 D4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -71415,7 +71775,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -71430,7 +71790,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A6</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -71452,7 +71812,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -71467,7 +71827,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A8</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -71489,7 +71849,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">Huh7 gNT</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -71504,7 +71864,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 E6</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -71526,7 +71886,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -71541,7 +71901,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 E8</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -71563,7 +71923,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -71578,7 +71938,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 B8</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -71600,7 +71960,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -71615,7 +71975,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 D5</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -71637,7 +71997,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -71652,7 +72012,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 D3</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -71674,7 +72034,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">khk</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -71689,7 +72049,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 D4</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -71711,7 +72071,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -71726,7 +72086,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -71763,7 +72123,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -71800,7 +72160,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -71837,7 +72197,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -71859,7 +72219,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -71874,7 +72234,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -71896,7 +72256,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -71911,7 +72271,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -71933,7 +72293,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -71948,7 +72308,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -71985,7 +72345,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -72022,7 +72382,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -72059,7 +72419,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -72118,7 +72478,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hek caspex</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -72128,12 +72488,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 I8</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -72155,7 +72515,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -72165,12 +72525,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -72192,7 +72552,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -72202,12 +72562,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A6</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -72229,7 +72589,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -72239,12 +72599,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A8</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -72266,7 +72626,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 gNT</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -72276,12 +72636,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 E6</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -72303,7 +72663,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -72313,12 +72673,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 E8</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -72340,7 +72700,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -72350,12 +72710,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 B8</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -72377,7 +72737,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -72387,12 +72747,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 D5</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -72414,7 +72774,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">Hek caspex</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -72429,7 +72789,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 D3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 I8</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -72451,7 +72811,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">khk</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -72466,7 +72826,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 D4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -72488,7 +72848,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -72503,7 +72863,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A6</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -72525,7 +72885,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -72540,7 +72900,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A8</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -72562,7 +72922,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">Huh7 gNT</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -72577,7 +72937,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 E6</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -72599,7 +72959,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -72614,7 +72974,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 E8</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -72636,7 +72996,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -72651,7 +73011,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 B8</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -72673,7 +73033,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -72688,7 +73048,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 D5</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -72710,7 +73070,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -72725,7 +73085,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 D3</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -72747,7 +73107,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">khk</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -72762,7 +73122,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 D4</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -72784,7 +73144,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -72799,7 +73159,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -72836,7 +73196,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -72873,7 +73233,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -72910,7 +73270,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -72932,7 +73292,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -72947,7 +73307,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -72969,7 +73329,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -72984,7 +73344,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -73006,7 +73366,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -73021,7 +73381,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -73058,7 +73418,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -73095,7 +73455,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -73132,7 +73492,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -73181,17 +73541,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:21:12.672Z</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -73201,24 +73561,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:21:12.672Z</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -73228,24 +73598,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:21:12.672Z</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -73256,23 +73636,33 @@
       <c r="E126" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:21:12.672Z</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -73283,23 +73673,33 @@
       <c r="E127" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:20:40.838Z</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -73309,24 +73709,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:20:40.838Z</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -73336,24 +73746,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:20:40.838Z</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -73364,23 +73784,33 @@
       <c r="E130" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:20:40.838Z</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -73391,13 +73821,23 @@
       <c r="E131" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:20:16.472Z</t>
+          <t xml:space="preserve">2026-09-07T15:21:12.672Z</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -73407,7 +73847,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -73424,7 +73864,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:20:16.472Z</t>
+          <t xml:space="preserve">2026-09-07T15:21:12.672Z</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -73434,7 +73874,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -73451,7 +73891,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:20:16.472Z</t>
+          <t xml:space="preserve">2026-09-07T15:21:12.672Z</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -73461,7 +73901,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -73478,7 +73918,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:20:16.472Z</t>
+          <t xml:space="preserve">2026-09-07T15:21:12.672Z</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -73488,7 +73928,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -73505,7 +73945,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:19:46.171Z</t>
+          <t xml:space="preserve">2026-09-07T15:20:40.838Z</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -73515,7 +73955,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 gNT</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -73532,7 +73972,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:19:46.171Z</t>
+          <t xml:space="preserve">2026-09-07T15:20:40.838Z</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -73542,7 +73982,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 gNT</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -73559,7 +73999,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:19:46.171Z</t>
+          <t xml:space="preserve">2026-09-07T15:20:40.838Z</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -73569,7 +74009,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 gNT</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -73586,7 +74026,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:19:46.171Z</t>
+          <t xml:space="preserve">2026-09-07T15:20:40.838Z</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -73596,7 +74036,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 gNT</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -73613,7 +74053,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:19:15.021Z</t>
+          <t xml:space="preserve">2026-09-07T15:20:16.472Z</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -73623,7 +74063,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -73640,7 +74080,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:19:15.021Z</t>
+          <t xml:space="preserve">2026-09-07T15:20:16.472Z</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -73650,7 +74090,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek atf3 ox rep3</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -73667,7 +74107,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:19:15.021Z</t>
+          <t xml:space="preserve">2026-09-07T15:20:16.472Z</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -73677,7 +74117,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -73694,7 +74134,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:19:15.021Z</t>
+          <t xml:space="preserve">2026-09-07T15:20:16.472Z</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -73704,7 +74144,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek atf3 ox rep3</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -73721,7 +74161,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:18:48.988Z</t>
+          <t xml:space="preserve">2026-09-07T15:19:46.171Z</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -73731,7 +74171,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">Huh7 gNT</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -73748,7 +74188,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:18:48.988Z</t>
+          <t xml:space="preserve">2026-09-07T15:19:46.171Z</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -73758,7 +74198,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">Huh7 gNT</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -73775,7 +74215,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:18:48.988Z</t>
+          <t xml:space="preserve">2026-09-07T15:19:46.171Z</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -73785,7 +74225,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">Huh7 gNT</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -73802,7 +74242,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:18:48.988Z</t>
+          <t xml:space="preserve">2026-09-07T15:19:46.171Z</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -73812,7 +74252,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">Huh7 gNT</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -73829,7 +74269,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:18:16.654Z</t>
+          <t xml:space="preserve">2026-09-07T15:19:15.021Z</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -73839,7 +74279,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -73856,7 +74296,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:18:16.654Z</t>
+          <t xml:space="preserve">2026-09-07T15:19:15.021Z</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -73866,7 +74306,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">hek atf3 ox rep3</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -73883,7 +74323,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:18:16.654Z</t>
+          <t xml:space="preserve">2026-09-07T15:19:15.021Z</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -73893,7 +74333,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -73910,7 +74350,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:18:16.654Z</t>
+          <t xml:space="preserve">2026-09-07T15:19:15.021Z</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -73920,7 +74360,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">hek atf3 ox rep3</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -73937,7 +74377,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:17:40.188Z</t>
+          <t xml:space="preserve">2026-09-07T15:18:48.988Z</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -73947,7 +74387,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -73964,7 +74404,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:17:40.188Z</t>
+          <t xml:space="preserve">2026-09-07T15:18:48.988Z</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -73974,7 +74414,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -73991,7 +74431,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:17:40.188Z</t>
+          <t xml:space="preserve">2026-09-07T15:18:48.988Z</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -74001,7 +74441,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -74018,25 +74458,241 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
+          <t xml:space="preserve">2026-09-07T15:18:48.988Z</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">added</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK 3xFLAG</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown device</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07T15:18:16.654Z</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">added</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown device</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07T15:18:16.654Z</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">added</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown device</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07T15:18:16.654Z</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">added</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown device</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07T15:18:16.654Z</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">added</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown device</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-07T15:17:40.188Z</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr">
+      <c r="B160" t="inlineStr">
         <is>
           <t xml:space="preserve">added</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr">
+      <c r="C160" t="inlineStr">
         <is>
           <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr">
+      <c r="D160" t="inlineStr">
         <is>
           <t xml:space="preserve">unknown device</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr">
+      <c r="E160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07T15:17:40.188Z</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">added</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK gNT</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown device</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07T15:17:40.188Z</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">added</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK gNT</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown device</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07T15:17:40.188Z</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">added</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK gNT</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown device</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
         </is>

--- a/cellstocks/exports/grid-roster.xlsx
+++ b/cellstocks/exports/grid-roster.xlsx
@@ -69567,17 +69567,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-17T08:55:14.517Z</t>
+          <t xml:space="preserve">2026-09-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -69588,23 +69588,33 @@
       <c r="E2" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 H4</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-17T08:54:58.904Z</t>
+          <t xml:space="preserve">2026-09-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">LnCap Canada</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -69615,23 +69625,33 @@
       <c r="E3" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 I5</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-17T08:54:36.349Z</t>
+          <t xml:space="preserve">2026-09-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -69642,13 +69662,23 @@
       <c r="E4" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 B4</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-17T08:54:15.940Z</t>
+          <t xml:space="preserve">2026-09-17T08:55:14.517Z</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -69658,7 +69688,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 gNT</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -69675,7 +69705,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-17T07:21:14.755Z</t>
+          <t xml:space="preserve">2026-09-17T08:54:58.904Z</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -69685,7 +69715,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -69702,7 +69732,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-17T07:20:55.862Z</t>
+          <t xml:space="preserve">2026-09-17T08:54:36.349Z</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -69712,7 +69742,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -69729,7 +69759,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-17T07:20:29.694Z</t>
+          <t xml:space="preserve">2026-09-17T08:54:15.940Z</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -69739,7 +69769,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">Huh7 gNT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -69756,7 +69786,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-17T07:18:28.049Z</t>
+          <t xml:space="preserve">2026-09-17T07:21:14.755Z</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -69766,7 +69796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -69783,7 +69813,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16T14:29:52.847Z</t>
+          <t xml:space="preserve">2026-09-17T07:20:55.862Z</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -69793,7 +69823,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gC4</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -69810,7 +69840,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16T14:29:52.847Z</t>
+          <t xml:space="preserve">2026-09-17T07:20:29.694Z</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -69820,7 +69850,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gC4</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -69837,7 +69867,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16T14:29:47.171Z</t>
+          <t xml:space="preserve">2026-09-17T07:18:28.049Z</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -69847,7 +69877,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gC3</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -69864,7 +69894,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16T14:29:47.171Z</t>
+          <t xml:space="preserve">2026-09-16T14:29:52.847Z</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -69874,7 +69904,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gC3</t>
+          <t xml:space="preserve">LNCX gC4</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -69891,7 +69921,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16T14:29:41.829Z</t>
+          <t xml:space="preserve">2026-09-16T14:29:52.847Z</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -69901,7 +69931,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gC2</t>
+          <t xml:space="preserve">LNCX gC4</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -69918,7 +69948,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16T14:29:41.829Z</t>
+          <t xml:space="preserve">2026-09-16T14:29:47.171Z</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -69928,7 +69958,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gC2</t>
+          <t xml:space="preserve">LNCX gC3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -69945,7 +69975,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16T14:28:53.172Z</t>
+          <t xml:space="preserve">2026-09-16T14:29:47.171Z</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -69955,7 +69985,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gC1</t>
+          <t xml:space="preserve">LNCX gC3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -69972,7 +70002,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16T14:28:52.574Z</t>
+          <t xml:space="preserve">2026-09-16T14:29:41.829Z</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -69982,7 +70012,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gC1</t>
+          <t xml:space="preserve">LNCX gC2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -69999,7 +70029,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16T14:28:36.457Z</t>
+          <t xml:space="preserve">2026-09-16T14:29:41.829Z</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -70009,7 +70039,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP3</t>
+          <t xml:space="preserve">LNCX gC2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -70026,7 +70056,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16T14:28:33.812Z</t>
+          <t xml:space="preserve">2026-09-16T14:28:53.172Z</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -70036,7 +70066,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP3</t>
+          <t xml:space="preserve">LNCX gC1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -70053,7 +70083,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16T14:28:18.882Z</t>
+          <t xml:space="preserve">2026-09-16T14:28:52.574Z</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -70063,7 +70093,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">LNCX gC1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -70080,7 +70110,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16T14:28:18.882Z</t>
+          <t xml:space="preserve">2026-09-16T14:28:36.457Z</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -70090,7 +70120,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">LNCX gP3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -70107,7 +70137,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16T14:28:08.430Z</t>
+          <t xml:space="preserve">2026-09-16T14:28:33.812Z</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -70117,7 +70147,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP1</t>
+          <t xml:space="preserve">LNCX gP3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -70134,7 +70164,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16T14:28:08.430Z</t>
+          <t xml:space="preserve">2026-09-16T14:28:18.882Z</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -70144,7 +70174,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP1</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -70161,7 +70191,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-15T08:59:29.978Z</t>
+          <t xml:space="preserve">2026-09-16T14:28:18.882Z</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -70171,7 +70201,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -70181,14 +70211,14 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-15T08:59:29.978Z</t>
+          <t xml:space="preserve">2026-09-16T14:28:08.430Z</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -70198,7 +70228,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX</t>
+          <t xml:space="preserve">LNCX gP1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -70208,14 +70238,14 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-15T08:59:29.978Z</t>
+          <t xml:space="preserve">2026-09-16T14:28:08.430Z</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -70225,7 +70255,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX</t>
+          <t xml:space="preserve">LNCX gP1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -70235,7 +70265,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
@@ -70262,7 +70292,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
@@ -70289,7 +70319,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
@@ -70316,14 +70346,14 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-15T08:59:01.686Z</t>
+          <t xml:space="preserve">2026-09-15T08:59:29.978Z</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -70333,7 +70363,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX</t>
+          <t xml:space="preserve">LUCX</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -70343,14 +70373,14 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-15T08:59:01.686Z</t>
+          <t xml:space="preserve">2026-09-15T08:59:29.978Z</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -70360,7 +70390,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX</t>
+          <t xml:space="preserve">LUCX</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -70370,14 +70400,14 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-15T08:59:01.686Z</t>
+          <t xml:space="preserve">2026-09-15T08:59:29.978Z</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -70387,7 +70417,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX</t>
+          <t xml:space="preserve">LUCX</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -70397,7 +70427,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
@@ -70424,7 +70454,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
@@ -70451,7 +70481,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
@@ -70478,24 +70508,24 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-11</t>
+          <t xml:space="preserve">2026-09-15T08:59:01.686Z</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">LNCX</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -70505,34 +70535,24 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 H1</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-11</t>
+          <t xml:space="preserve">2026-09-15T08:59:01.686Z</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">LNCX</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -70543,33 +70563,23 @@
       <c r="E37" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 H1</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-10</t>
+          <t xml:space="preserve">2026-09-15T08:59:01.686Z</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LNCX</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -70579,24 +70589,14 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 F6</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-10</t>
+          <t xml:space="preserve">2026-09-11</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -70606,7 +70606,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">kkk</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -70616,12 +70616,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 F6</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 H1</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -70633,17 +70633,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09T13:48:02.210Z</t>
+          <t xml:space="preserve">2026-09-11</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">deneme</t>
+          <t xml:space="preserve">kkk</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -70653,24 +70653,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 H1</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09T13:48:02.210Z</t>
+          <t xml:space="preserve">2026-09-10</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">deneme</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -70680,24 +70690,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 F6</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09T04:57:21.749Z</t>
+          <t xml:space="preserve">2026-09-10</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -70707,14 +70727,24 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 F6</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09T04:57:21.749Z</t>
+          <t xml:space="preserve">2026-09-09T13:48:02.210Z</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -70724,7 +70754,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">deneme</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -70734,14 +70764,14 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09T04:57:19.918Z</t>
+          <t xml:space="preserve">2026-09-09T13:48:02.210Z</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -70751,7 +70781,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">deneme</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -70761,14 +70791,14 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09T04:57:19.918Z</t>
+          <t xml:space="preserve">2026-09-09T04:57:21.749Z</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -70788,14 +70818,14 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09T04:57:16.692Z</t>
+          <t xml:space="preserve">2026-09-09T04:57:21.749Z</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -70815,14 +70845,14 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09T04:57:16.692Z</t>
+          <t xml:space="preserve">2026-09-09T04:57:19.918Z</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -70842,24 +70872,24 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-09T04:57:19.918Z</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">kkk</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -70869,34 +70899,24 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-09T04:57:16.692Z</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">kkk</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -70907,33 +70927,23 @@
       <c r="E49" t="inlineStr">
         <is>
           <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-09T04:57:16.692Z</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">kkk</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -70943,17 +70953,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
@@ -70970,7 +70970,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -70985,7 +70985,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -71007,7 +71007,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -71022,7 +71022,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 H3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -71044,7 +71044,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -71059,7 +71059,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 H2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -71081,7 +71081,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">deneme</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -71096,7 +71096,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 B3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -71118,7 +71118,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">kkk</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -71128,12 +71128,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 H3</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -71155,7 +71155,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">kkk</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -71165,12 +71165,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 H2</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -71192,7 +71192,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">deneme</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -71202,12 +71202,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 B3</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -71229,7 +71229,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -71244,7 +71244,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -71266,7 +71266,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -71281,7 +71281,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 H3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -71303,7 +71303,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -71318,7 +71318,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 H2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -71340,7 +71340,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">deneme</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -71355,7 +71355,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 B3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -71367,17 +71367,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T20:53:21.794Z</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">khk</t>
+          <t xml:space="preserve">kkk</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -71387,24 +71387,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 H3</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T20:53:21.794Z</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">khk</t>
+          <t xml:space="preserve">kkk</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -71415,23 +71425,33 @@
       <c r="E63" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 H2</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T20:05:13.592Z</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">deneme</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -71441,14 +71461,24 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 2 B3</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T20:05:13.592Z</t>
+          <t xml:space="preserve">2026-09-08T20:53:21.794Z</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -71458,7 +71488,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">khk</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -71475,7 +71505,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T20:05:13.592Z</t>
+          <t xml:space="preserve">2026-09-08T20:53:21.794Z</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -71485,7 +71515,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">khk</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -71495,7 +71525,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
@@ -71522,7 +71552,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
@@ -71549,7 +71579,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
@@ -71576,14 +71606,14 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T18:36:51.554Z</t>
+          <t xml:space="preserve">2026-09-08T20:05:13.592Z</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -71593,7 +71623,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -71603,14 +71633,14 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T18:36:51.554Z</t>
+          <t xml:space="preserve">2026-09-08T20:05:13.592Z</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -71620,7 +71650,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -71637,7 +71667,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T11:09:47.786Z</t>
+          <t xml:space="preserve">2026-09-08T20:05:13.592Z</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -71647,7 +71677,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hek caspex</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -71657,14 +71687,14 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T11:09:47.786Z</t>
+          <t xml:space="preserve">2026-09-08T18:36:51.554Z</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -71674,7 +71704,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hek caspex</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -71684,24 +71714,24 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-08T18:36:51.554Z</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hek caspex</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -71711,34 +71741,24 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 I8</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-08T11:09:47.786Z</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">Hek caspex</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -71749,33 +71769,23 @@
       <c r="E75" t="inlineStr">
         <is>
           <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-08T11:09:47.786Z</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">Hek caspex</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -71785,17 +71795,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A6</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
@@ -71812,7 +71812,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">Hek caspex</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -71827,7 +71827,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A8</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 I8</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -71849,7 +71849,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 gNT</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -71864,7 +71864,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 E6</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -71886,7 +71886,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -71901,7 +71901,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 E8</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A6</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -71923,7 +71923,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -71938,7 +71938,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 B8</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A8</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -71960,7 +71960,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">Huh7 gNT</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -71975,7 +71975,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 D5</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 E6</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -71997,7 +71997,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -72012,7 +72012,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 D3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 E8</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -72034,7 +72034,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">khk</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -72049,7 +72049,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 D4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 B8</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -72071,7 +72071,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -72086,7 +72086,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 D5</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -72108,7 +72108,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -72123,7 +72123,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 D3</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -72145,7 +72145,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">khk</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -72160,7 +72160,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 D4</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -72182,7 +72182,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -72197,7 +72197,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -72219,7 +72219,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -72234,7 +72234,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -72271,7 +72271,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -72293,7 +72293,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -72308,7 +72308,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -72330,7 +72330,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -72345,7 +72345,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -72382,7 +72382,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -72404,7 +72404,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -72419,7 +72419,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -72456,7 +72456,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -72530,7 +72530,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -72552,7 +72552,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -72567,7 +72567,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -72604,7 +72604,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -72641,7 +72641,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -72663,7 +72663,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -72678,7 +72678,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -72715,7 +72715,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -72752,7 +72752,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -72774,7 +72774,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hek caspex</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -72784,12 +72784,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 I8</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -72811,7 +72811,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -72821,12 +72821,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -72848,7 +72848,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -72858,12 +72858,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A6</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -72885,7 +72885,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">Hek caspex</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -72900,7 +72900,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A8</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 I8</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -72922,7 +72922,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 gNT</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -72937,7 +72937,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 E6</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -72959,7 +72959,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -72974,7 +72974,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 E8</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A6</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -72996,7 +72996,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -73011,7 +73011,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 B8</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A8</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -73033,7 +73033,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">Huh7 gNT</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -73048,7 +73048,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 D5</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 E6</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -73070,7 +73070,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -73085,7 +73085,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 D3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 E8</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -73107,7 +73107,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">khk</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -73122,7 +73122,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 D4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 B8</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -73144,7 +73144,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -73159,7 +73159,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 D5</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -73181,7 +73181,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -73196,7 +73196,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 D3</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -73218,7 +73218,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">khk</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -73233,7 +73233,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 D4</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -73255,7 +73255,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -73270,7 +73270,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -73292,7 +73292,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -73307,7 +73307,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -73344,7 +73344,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -73366,7 +73366,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -73381,7 +73381,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -73403,7 +73403,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -73418,7 +73418,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -73455,7 +73455,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -73477,7 +73477,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -73492,7 +73492,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -73529,7 +73529,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -73603,7 +73603,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -73625,7 +73625,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -73640,7 +73640,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -73677,7 +73677,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -73714,7 +73714,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -73736,7 +73736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -73751,7 +73751,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -73788,7 +73788,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -73825,7 +73825,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -73837,17 +73837,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:21:12.672Z</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -73857,24 +73857,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:21:12.672Z</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -73884,24 +73894,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:21:12.672Z</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -73912,6 +73932,16 @@
       <c r="E134" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
@@ -73938,14 +73968,14 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:20:40.838Z</t>
+          <t xml:space="preserve">2026-09-07T15:21:12.672Z</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -73955,7 +73985,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -73972,7 +74002,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:20:40.838Z</t>
+          <t xml:space="preserve">2026-09-07T15:21:12.672Z</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -73982,7 +74012,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -73992,14 +74022,14 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:20:40.838Z</t>
+          <t xml:space="preserve">2026-09-07T15:21:12.672Z</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -74009,7 +74039,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -74046,14 +74076,14 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:20:16.472Z</t>
+          <t xml:space="preserve">2026-09-07T15:20:40.838Z</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -74063,7 +74093,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -74080,7 +74110,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:20:16.472Z</t>
+          <t xml:space="preserve">2026-09-07T15:20:40.838Z</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -74090,7 +74120,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -74100,14 +74130,14 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:20:16.472Z</t>
+          <t xml:space="preserve">2026-09-07T15:20:40.838Z</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -74117,7 +74147,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -74154,14 +74184,14 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:19:46.171Z</t>
+          <t xml:space="preserve">2026-09-07T15:20:16.472Z</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -74171,7 +74201,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 gNT</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -74188,7 +74218,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:19:46.171Z</t>
+          <t xml:space="preserve">2026-09-07T15:20:16.472Z</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -74198,7 +74228,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 gNT</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -74208,14 +74238,14 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:19:46.171Z</t>
+          <t xml:space="preserve">2026-09-07T15:20:16.472Z</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -74225,7 +74255,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 gNT</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -74262,14 +74292,14 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:19:15.021Z</t>
+          <t xml:space="preserve">2026-09-07T15:19:46.171Z</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -74279,7 +74309,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">Huh7 gNT</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -74296,7 +74326,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:19:15.021Z</t>
+          <t xml:space="preserve">2026-09-07T15:19:46.171Z</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -74306,7 +74336,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek atf3 ox rep3</t>
+          <t xml:space="preserve">Huh7 gNT</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -74316,14 +74346,14 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:19:15.021Z</t>
+          <t xml:space="preserve">2026-09-07T15:19:46.171Z</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -74333,7 +74363,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">Huh7 gNT</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -74360,7 +74390,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek atf3 ox rep3</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -74370,14 +74400,14 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:18:48.988Z</t>
+          <t xml:space="preserve">2026-09-07T15:19:15.021Z</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -74387,7 +74417,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">hek atf3 ox rep3</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -74404,7 +74434,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:18:48.988Z</t>
+          <t xml:space="preserve">2026-09-07T15:19:15.021Z</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -74414,7 +74444,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -74424,14 +74454,14 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:18:48.988Z</t>
+          <t xml:space="preserve">2026-09-07T15:19:15.021Z</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -74441,7 +74471,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">hek atf3 ox rep3</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -74478,14 +74508,14 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:18:16.654Z</t>
+          <t xml:space="preserve">2026-09-07T15:18:48.988Z</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -74495,7 +74525,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -74512,7 +74542,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:18:16.654Z</t>
+          <t xml:space="preserve">2026-09-07T15:18:48.988Z</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -74522,7 +74552,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -74532,14 +74562,14 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:18:16.654Z</t>
+          <t xml:space="preserve">2026-09-07T15:18:48.988Z</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -74549,7 +74579,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -74586,14 +74616,14 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:17:40.188Z</t>
+          <t xml:space="preserve">2026-09-07T15:18:16.654Z</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -74603,7 +74633,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -74620,7 +74650,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:17:40.188Z</t>
+          <t xml:space="preserve">2026-09-07T15:18:16.654Z</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -74630,7 +74660,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -74640,14 +74670,14 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:17:40.188Z</t>
+          <t xml:space="preserve">2026-09-07T15:18:16.654Z</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -74657,7 +74687,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -74693,6 +74723,87 @@
         </is>
       </c>
       <c r="E163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07T15:17:40.188Z</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">added</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK gNT</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown device</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07T15:17:40.188Z</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">added</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK gNT</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown device</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07T15:17:40.188Z</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">added</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK gNT</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown device</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
         </is>

--- a/cellstocks/exports/grid-roster.xlsx
+++ b/cellstocks/exports/grid-roster.xlsx
@@ -66235,61 +66235,6 @@
           <t xml:space="preserve">D3</t>
         </is>
       </c>
-      <c r="C355" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cell</t>
-        </is>
-      </c>
-      <c r="E355" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Huh7</t>
-        </is>
-      </c>
-      <c r="F355" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FLAG</t>
-        </is>
-      </c>
-      <c r="G355" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Par</t>
-        </is>
-      </c>
-      <c r="H355" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No Casp</t>
-        </is>
-      </c>
-      <c r="I355" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No guide/sh</t>
-        </is>
-      </c>
-      <c r="J355" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p19</t>
-        </is>
-      </c>
-      <c r="K355" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="L355" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-17</t>
-        </is>
-      </c>
-      <c r="M355" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-17</t>
-        </is>
-      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -75949,17 +75894,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-01T15:26:42.270Z</t>
+          <t xml:space="preserve">2026-10-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -75970,23 +75915,33 @@
       <c r="E2" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A7</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-01T15:26:42.270Z</t>
+          <t xml:space="preserve">2026-10-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -75997,6 +75952,16 @@
       <c r="E3" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 D3</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
@@ -76084,17 +76049,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-01</t>
+          <t xml:space="preserve">2026-10-01T15:26:42.270Z</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -76105,33 +76070,23 @@
       <c r="E7" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 I4</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-01</t>
+          <t xml:space="preserve">2026-10-01T15:26:42.270Z</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -76142,33 +76097,23 @@
       <c r="E8" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 D9</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-29T12:51:02.649Z</t>
+          <t xml:space="preserve">2026-10-01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX gC4</t>
+          <t xml:space="preserve">LNCX</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -76179,23 +76124,33 @@
       <c r="E9" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 I4</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-29T12:50:54.365Z</t>
+          <t xml:space="preserve">2026-10-01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX gC3</t>
+          <t xml:space="preserve">LNCX</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -76206,13 +76161,23 @@
       <c r="E10" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 D9</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-29T12:50:42.027Z</t>
+          <t xml:space="preserve">2026-09-29T12:51:02.649Z</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -76222,7 +76187,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX gC2</t>
+          <t xml:space="preserve">LUCX gC4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -76239,7 +76204,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-29T12:50:21.886Z</t>
+          <t xml:space="preserve">2026-09-29T12:50:54.365Z</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -76249,7 +76214,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX gC1</t>
+          <t xml:space="preserve">LUCX gC3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -76266,7 +76231,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-29T12:50:10.233Z</t>
+          <t xml:space="preserve">2026-09-29T12:50:42.027Z</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -76276,7 +76241,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX gP3</t>
+          <t xml:space="preserve">LUCX gC2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -76293,7 +76258,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-29T12:49:59.714Z</t>
+          <t xml:space="preserve">2026-09-29T12:50:21.886Z</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -76303,7 +76268,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX gP1</t>
+          <t xml:space="preserve">LUCX gC1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -76320,17 +76285,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-29</t>
+          <t xml:space="preserve">2026-09-29T12:50:10.233Z</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">LUCX gP3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -76341,33 +76306,23 @@
       <c r="E15" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 D2</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-29</t>
+          <t xml:space="preserve">2026-09-29T12:49:59.714Z</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX</t>
+          <t xml:space="preserve">LUCX gP1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -76378,23 +76333,13 @@
       <c r="E16" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 H7</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-24</t>
+          <t xml:space="preserve">2026-09-29</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -76404,12 +76349,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown device</t>
+          <t xml:space="preserve">Umut</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -76419,7 +76364,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 H4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 D2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -76431,7 +76376,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-24</t>
+          <t xml:space="preserve">2026-09-29</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -76441,12 +76386,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada</t>
+          <t xml:space="preserve">LUCX</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown device</t>
+          <t xml:space="preserve">Umut</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -76456,7 +76401,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 I5</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 H7</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -76478,7 +76423,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -76493,7 +76438,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 B4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 H4</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -76505,17 +76450,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-17T08:55:14.517Z</t>
+          <t xml:space="preserve">2026-09-24</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">LnCap Canada</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -76526,23 +76471,33 @@
       <c r="E20" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 I5</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-17T08:54:58.904Z</t>
+          <t xml:space="preserve">2026-09-24</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -76553,13 +76508,23 @@
       <c r="E21" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 B4</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-17T08:54:36.349Z</t>
+          <t xml:space="preserve">2026-09-17T08:55:14.517Z</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -76569,7 +76534,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -76586,7 +76551,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-17T08:54:15.940Z</t>
+          <t xml:space="preserve">2026-09-17T08:54:58.904Z</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -76596,7 +76561,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 gNT</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -76613,7 +76578,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-17T07:21:14.755Z</t>
+          <t xml:space="preserve">2026-09-17T08:54:36.349Z</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -76623,7 +76588,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -76640,7 +76605,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-17T07:20:55.862Z</t>
+          <t xml:space="preserve">2026-09-17T08:54:15.940Z</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -76650,7 +76615,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">Huh7 gNT</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -76667,7 +76632,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-17T07:20:29.694Z</t>
+          <t xml:space="preserve">2026-09-17T07:21:14.755Z</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -76677,7 +76642,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -76694,7 +76659,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-17T07:18:28.049Z</t>
+          <t xml:space="preserve">2026-09-17T07:20:55.862Z</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -76704,7 +76669,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -76721,7 +76686,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16T14:29:52.847Z</t>
+          <t xml:space="preserve">2026-09-17T07:20:29.694Z</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -76731,7 +76696,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gC4</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -76748,7 +76713,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16T14:29:52.847Z</t>
+          <t xml:space="preserve">2026-09-17T07:18:28.049Z</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -76758,7 +76723,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gC4</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -76775,7 +76740,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16T14:29:47.171Z</t>
+          <t xml:space="preserve">2026-09-16T14:29:52.847Z</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -76785,7 +76750,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gC3</t>
+          <t xml:space="preserve">LNCX gC4</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -76802,7 +76767,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16T14:29:47.171Z</t>
+          <t xml:space="preserve">2026-09-16T14:29:52.847Z</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -76812,7 +76777,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gC3</t>
+          <t xml:space="preserve">LNCX gC4</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -76829,7 +76794,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16T14:29:41.829Z</t>
+          <t xml:space="preserve">2026-09-16T14:29:47.171Z</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -76839,7 +76804,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gC2</t>
+          <t xml:space="preserve">LNCX gC3</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -76856,7 +76821,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16T14:29:41.829Z</t>
+          <t xml:space="preserve">2026-09-16T14:29:47.171Z</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -76866,7 +76831,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gC2</t>
+          <t xml:space="preserve">LNCX gC3</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -76883,7 +76848,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16T14:28:53.172Z</t>
+          <t xml:space="preserve">2026-09-16T14:29:41.829Z</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -76893,7 +76858,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gC1</t>
+          <t xml:space="preserve">LNCX gC2</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -76910,7 +76875,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16T14:28:52.574Z</t>
+          <t xml:space="preserve">2026-09-16T14:29:41.829Z</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -76920,7 +76885,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gC1</t>
+          <t xml:space="preserve">LNCX gC2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -76937,7 +76902,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16T14:28:36.457Z</t>
+          <t xml:space="preserve">2026-09-16T14:28:53.172Z</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -76947,7 +76912,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP3</t>
+          <t xml:space="preserve">LNCX gC1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -76964,7 +76929,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16T14:28:33.812Z</t>
+          <t xml:space="preserve">2026-09-16T14:28:52.574Z</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -76974,7 +76939,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP3</t>
+          <t xml:space="preserve">LNCX gC1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -76991,7 +76956,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16T14:28:18.882Z</t>
+          <t xml:space="preserve">2026-09-16T14:28:36.457Z</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -77001,7 +76966,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">LNCX gP3</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -77018,7 +76983,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16T14:28:18.882Z</t>
+          <t xml:space="preserve">2026-09-16T14:28:33.812Z</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -77028,7 +76993,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">LNCX gP3</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -77045,7 +77010,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16T14:28:08.430Z</t>
+          <t xml:space="preserve">2026-09-16T14:28:18.882Z</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -77055,7 +77020,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP1</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -77072,7 +77037,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16T14:28:08.430Z</t>
+          <t xml:space="preserve">2026-09-16T14:28:18.882Z</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -77082,7 +77047,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP1</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -77099,7 +77064,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-15T08:59:29.978Z</t>
+          <t xml:space="preserve">2026-09-16T14:28:08.430Z</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -77109,7 +77074,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX</t>
+          <t xml:space="preserve">LNCX gP1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -77119,14 +77084,14 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-15T08:59:29.978Z</t>
+          <t xml:space="preserve">2026-09-16T14:28:08.430Z</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -77136,7 +77101,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX</t>
+          <t xml:space="preserve">LNCX gP1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -77146,7 +77111,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
@@ -77200,7 +77165,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
@@ -77227,7 +77192,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
@@ -77261,7 +77226,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-15T08:59:01.686Z</t>
+          <t xml:space="preserve">2026-09-15T08:59:29.978Z</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -77271,7 +77236,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX</t>
+          <t xml:space="preserve">LUCX</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -77281,14 +77246,14 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-15T08:59:01.686Z</t>
+          <t xml:space="preserve">2026-09-15T08:59:29.978Z</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -77298,7 +77263,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX</t>
+          <t xml:space="preserve">LUCX</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -77308,7 +77273,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
@@ -77362,7 +77327,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
@@ -77389,7 +77354,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
@@ -77423,17 +77388,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-11</t>
+          <t xml:space="preserve">2026-09-15T08:59:01.686Z</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">LNCX</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -77443,34 +77408,24 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 H1</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-11</t>
+          <t xml:space="preserve">2026-09-15T08:59:01.686Z</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">LNCX</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -77481,23 +77436,13 @@
       <c r="E55" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 H1</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-10</t>
+          <t xml:space="preserve">2026-09-11</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -77507,7 +77452,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">kkk</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -77522,7 +77467,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 F6</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 H1</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -77534,7 +77479,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-10</t>
+          <t xml:space="preserve">2026-09-11</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -77544,7 +77489,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">kkk</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -77559,7 +77504,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 F6</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 H1</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -77571,17 +77516,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09T13:48:02.210Z</t>
+          <t xml:space="preserve">2026-09-10</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">deneme</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -77592,23 +77537,33 @@
       <c r="E58" t="inlineStr">
         <is>
           <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 F6</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09T13:48:02.210Z</t>
+          <t xml:space="preserve">2026-09-10</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">deneme</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -77619,13 +77574,23 @@
       <c r="E59" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 F6</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09T04:57:21.749Z</t>
+          <t xml:space="preserve">2026-09-09T13:48:02.210Z</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -77635,7 +77600,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">deneme</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -77652,7 +77617,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09T04:57:21.749Z</t>
+          <t xml:space="preserve">2026-09-09T13:48:02.210Z</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -77662,7 +77627,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">deneme</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -77679,7 +77644,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09T04:57:19.918Z</t>
+          <t xml:space="preserve">2026-09-09T04:57:21.749Z</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -77706,7 +77671,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09T04:57:19.918Z</t>
+          <t xml:space="preserve">2026-09-09T04:57:21.749Z</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -77733,7 +77698,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09T04:57:16.692Z</t>
+          <t xml:space="preserve">2026-09-09T04:57:19.918Z</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -77760,7 +77725,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09T04:57:16.692Z</t>
+          <t xml:space="preserve">2026-09-09T04:57:19.918Z</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -77787,17 +77752,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-09T04:57:16.692Z</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">kkk</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -77808,33 +77773,23 @@
       <c r="E66" t="inlineStr">
         <is>
           <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-09T04:57:16.692Z</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">kkk</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -77844,17 +77799,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
@@ -77886,7 +77831,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -77908,7 +77853,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -77923,7 +77868,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -77945,7 +77890,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -77960,7 +77905,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 H3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -77982,7 +77927,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -77997,7 +77942,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 H2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -78019,7 +77964,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">deneme</t>
+          <t xml:space="preserve">kkk</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -78034,7 +77979,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 B3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 H3</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -78056,7 +78001,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">kkk</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -78066,12 +78011,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 H2</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -78093,7 +78038,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">deneme</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -78103,12 +78048,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 B3</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -78145,7 +78090,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -78167,7 +78112,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -78182,7 +78127,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -78204,7 +78149,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -78219,7 +78164,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 H3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -78241,7 +78186,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -78256,7 +78201,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 H2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -78278,7 +78223,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">deneme</t>
+          <t xml:space="preserve">kkk</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -78293,7 +78238,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 B3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 H3</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -78305,17 +78250,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T20:53:21.794Z</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">khk</t>
+          <t xml:space="preserve">kkk</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -78325,24 +78270,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 H2</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T20:53:21.794Z</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">khk</t>
+          <t xml:space="preserve">deneme</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -78353,13 +78308,23 @@
       <c r="E81" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 2 B3</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T20:05:13.592Z</t>
+          <t xml:space="preserve">2026-09-08T20:53:21.794Z</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -78369,7 +78334,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">khk</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -78386,7 +78351,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T20:05:13.592Z</t>
+          <t xml:space="preserve">2026-09-08T20:53:21.794Z</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -78396,7 +78361,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">khk</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -78406,7 +78371,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
@@ -78460,7 +78425,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
@@ -78487,7 +78452,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
@@ -78521,7 +78486,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T18:36:51.554Z</t>
+          <t xml:space="preserve">2026-09-08T20:05:13.592Z</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -78531,7 +78496,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -78541,14 +78506,14 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T18:36:51.554Z</t>
+          <t xml:space="preserve">2026-09-08T20:05:13.592Z</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -78558,7 +78523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -78575,7 +78540,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T11:09:47.786Z</t>
+          <t xml:space="preserve">2026-09-08T18:36:51.554Z</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -78585,7 +78550,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hek caspex</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -78602,7 +78567,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T11:09:47.786Z</t>
+          <t xml:space="preserve">2026-09-08T18:36:51.554Z</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -78612,7 +78577,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hek caspex</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -78629,12 +78594,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-08T11:09:47.786Z</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -78650,33 +78615,23 @@
       <c r="E92" t="inlineStr">
         <is>
           <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 I8</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-08T11:09:47.786Z</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">Hek caspex</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -78686,17 +78641,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
@@ -78713,7 +78658,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">Hek caspex</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -78728,7 +78673,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A6</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 I8</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -78750,7 +78695,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -78765,7 +78710,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A8</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -78787,7 +78732,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 gNT</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -78802,7 +78747,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 E6</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A6</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -78824,7 +78769,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -78839,7 +78784,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 E8</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A8</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -78861,7 +78806,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">Huh7 gNT</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -78876,7 +78821,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 B8</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 E6</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -78898,7 +78843,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -78913,7 +78858,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 D5</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 E8</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -78935,7 +78880,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -78950,7 +78895,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 D3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 B8</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -78972,7 +78917,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">khk</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -78987,7 +78932,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 D4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 D5</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -79009,7 +78954,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -79024,7 +78969,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 D3</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -79046,7 +78991,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">khk</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -79061,7 +79006,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 D4</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -79083,7 +79028,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -79098,7 +79043,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -79135,7 +79080,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -79157,7 +79102,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -79172,7 +79117,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -79209,7 +79154,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -79305,7 +79250,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -79320,7 +79265,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -79357,7 +79302,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -79394,7 +79339,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -79431,7 +79376,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -79468,7 +79413,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -79490,7 +79435,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -79505,7 +79450,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -79542,7 +79487,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -79564,7 +79509,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -79579,7 +79524,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -79712,7 +79657,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hek caspex</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -79722,12 +79667,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 I8</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -79749,7 +79694,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -79759,12 +79704,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -79786,7 +79731,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">Hek caspex</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -79801,7 +79746,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A6</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 I8</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -79823,7 +79768,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -79838,7 +79783,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A8</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -79860,7 +79805,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 gNT</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -79875,7 +79820,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 E6</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A6</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -79897,7 +79842,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -79912,7 +79857,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 E8</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A8</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -79934,7 +79879,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">Huh7 gNT</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -79949,7 +79894,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 B8</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 E6</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -79971,7 +79916,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -79986,7 +79931,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 D5</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 E8</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -80008,7 +79953,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -80023,7 +79968,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 D3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 B8</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -80045,7 +79990,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve">khk</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -80060,7 +80005,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 D4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 D5</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -80082,7 +80027,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -80097,7 +80042,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 D3</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -80119,7 +80064,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">khk</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -80134,7 +80079,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 D4</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -80156,7 +80101,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -80171,7 +80116,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -80208,7 +80153,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -80230,7 +80175,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -80245,7 +80190,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -80282,7 +80227,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -80378,7 +80323,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -80393,7 +80338,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -80430,7 +80375,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -80467,7 +80412,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -80504,7 +80449,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -80541,7 +80486,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -80563,7 +80508,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -80578,7 +80523,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -80615,7 +80560,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A2</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -80637,7 +80582,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -80652,7 +80597,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A1</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -80775,17 +80720,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:21:12.672Z</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -80795,24 +80740,34 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A3</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:21:12.672Z</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -80822,7 +80777,17 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 2 A4</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
@@ -80849,7 +80814,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
@@ -80876,14 +80841,14 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:20:40.838Z</t>
+          <t xml:space="preserve">2026-09-07T15:21:12.672Z</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -80893,7 +80858,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -80903,14 +80868,14 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:20:40.838Z</t>
+          <t xml:space="preserve">2026-09-07T15:21:12.672Z</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -80920,7 +80885,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -80930,7 +80895,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
@@ -80957,7 +80922,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
@@ -80984,14 +80949,14 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:20:16.472Z</t>
+          <t xml:space="preserve">2026-09-07T15:20:40.838Z</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -81001,7 +80966,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -81011,14 +80976,14 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:20:16.472Z</t>
+          <t xml:space="preserve">2026-09-07T15:20:40.838Z</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -81028,7 +80993,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -81038,7 +81003,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
@@ -81065,7 +81030,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
@@ -81092,14 +81057,14 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:19:46.171Z</t>
+          <t xml:space="preserve">2026-09-07T15:20:16.472Z</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -81109,7 +81074,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 gNT</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -81119,14 +81084,14 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:19:46.171Z</t>
+          <t xml:space="preserve">2026-09-07T15:20:16.472Z</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -81136,7 +81101,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 gNT</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -81146,7 +81111,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
@@ -81173,7 +81138,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
@@ -81200,14 +81165,14 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:19:15.021Z</t>
+          <t xml:space="preserve">2026-09-07T15:19:46.171Z</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -81217,7 +81182,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">Huh7 gNT</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -81227,14 +81192,14 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:19:15.021Z</t>
+          <t xml:space="preserve">2026-09-07T15:19:46.171Z</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -81244,7 +81209,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek atf3 ox rep3</t>
+          <t xml:space="preserve">Huh7 gNT</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -81254,7 +81219,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
@@ -81281,7 +81246,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
@@ -81308,14 +81273,14 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:18:48.988Z</t>
+          <t xml:space="preserve">2026-09-07T15:19:15.021Z</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -81325,7 +81290,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -81335,14 +81300,14 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:18:48.988Z</t>
+          <t xml:space="preserve">2026-09-07T15:19:15.021Z</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -81352,7 +81317,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">hek atf3 ox rep3</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -81362,7 +81327,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
@@ -81389,7 +81354,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
@@ -81416,14 +81381,14 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:18:16.654Z</t>
+          <t xml:space="preserve">2026-09-07T15:18:48.988Z</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -81433,7 +81398,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -81443,14 +81408,14 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:18:16.654Z</t>
+          <t xml:space="preserve">2026-09-07T15:18:48.988Z</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -81460,7 +81425,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -81470,7 +81435,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
@@ -81497,7 +81462,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
@@ -81524,14 +81489,14 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:17:40.188Z</t>
+          <t xml:space="preserve">2026-09-07T15:18:16.654Z</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -81541,7 +81506,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -81551,14 +81516,14 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:17:40.188Z</t>
+          <t xml:space="preserve">2026-09-07T15:18:16.654Z</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -81568,7 +81533,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -81578,7 +81543,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
@@ -81605,7 +81570,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
@@ -81631,6 +81596,60 @@
         </is>
       </c>
       <c r="E181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07T15:17:40.188Z</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">added</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK gNT</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown device</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07T15:17:40.188Z</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">added</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK gNT</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown device</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
         </is>
